--- a/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9740_escuela-basica-republica-de-las-filipinas_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1333F369-7CAA-4EEB-B462-82E72275DBD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB78B7C4-089E-4C6D-8DB8-A1E4463C8497}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B67942-5A93-4155-A66D-1279D2DF1F93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FBBA114-4E4C-4E95-82B7-6B245C377452}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF3F7F00-A227-4503-ACBB-EAF0AE2BCE41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFAD31AE-925F-49DC-B334-D08AB42FA3D9}"/>
 </file>